--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,38 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R4" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350421</v>
+        <v>127351442</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,34 +977,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863799</v>
+        <v>863724</v>
       </c>
       <c r="R5" t="n">
-        <v>7421075</v>
+        <v>7421178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127351426</v>
+        <v>127351480</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863721</v>
+        <v>863715</v>
       </c>
       <c r="R6" t="n">
-        <v>7421272</v>
+        <v>7421176</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127351480</v>
+        <v>127351426</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863715</v>
+        <v>863721</v>
       </c>
       <c r="R7" t="n">
-        <v>7421176</v>
+        <v>7421272</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1657,32 +1657,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127350404</v>
+        <v>127350403</v>
       </c>
       <c r="B12" t="n">
-        <v>98463</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>863898</v>
+        <v>863657</v>
       </c>
       <c r="R12" t="n">
-        <v>7420759</v>
+        <v>7421213</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1754,32 +1754,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127350403</v>
+        <v>127350404</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>98464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>863657</v>
+        <v>863898</v>
       </c>
       <c r="R13" t="n">
-        <v>7421213</v>
+        <v>7420759</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -1657,32 +1657,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127350403</v>
+        <v>127350404</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>98464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>863657</v>
+        <v>863898</v>
       </c>
       <c r="R12" t="n">
-        <v>7421213</v>
+        <v>7420759</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1754,32 +1754,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127350404</v>
+        <v>127350403</v>
       </c>
       <c r="B13" t="n">
-        <v>98464</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>863898</v>
+        <v>863657</v>
       </c>
       <c r="R13" t="n">
-        <v>7420759</v>
+        <v>7421213</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127350421</v>
+        <v>127351442</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863799</v>
+        <v>863724</v>
       </c>
       <c r="R4" t="n">
-        <v>7421075</v>
+        <v>7421178</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,38 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R5" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127351480</v>
+        <v>127351426</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863715</v>
+        <v>863721</v>
       </c>
       <c r="R6" t="n">
-        <v>7421176</v>
+        <v>7421272</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127351426</v>
+        <v>127351480</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863721</v>
+        <v>863715</v>
       </c>
       <c r="R7" t="n">
-        <v>7421272</v>
+        <v>7421176</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1657,32 +1657,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127350404</v>
+        <v>127350403</v>
       </c>
       <c r="B12" t="n">
-        <v>98464</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>863898</v>
+        <v>863657</v>
       </c>
       <c r="R12" t="n">
-        <v>7420759</v>
+        <v>7421213</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1754,32 +1754,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127350403</v>
+        <v>127350404</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>98464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>863657</v>
+        <v>863898</v>
       </c>
       <c r="R13" t="n">
-        <v>7421213</v>
+        <v>7420759</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127350411</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127350423</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127351442</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127350421</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127351426</v>
+        <v>127351480</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863721</v>
+        <v>863715</v>
       </c>
       <c r="R6" t="n">
-        <v>7421272</v>
+        <v>7421176</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127351480</v>
+        <v>127351426</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863715</v>
+        <v>863721</v>
       </c>
       <c r="R7" t="n">
-        <v>7421176</v>
+        <v>7421272</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>127350422</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>127350424</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>127350410</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127350412</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127350404</v>
       </c>
       <c r="B12" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>127350403</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,38 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R4" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350421</v>
+        <v>127351442</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,34 +977,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863799</v>
+        <v>863724</v>
       </c>
       <c r="R5" t="n">
-        <v>7421075</v>
+        <v>7421178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127351480</v>
+        <v>127351426</v>
       </c>
       <c r="B6" t="n">
         <v>79018</v>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863715</v>
+        <v>863721</v>
       </c>
       <c r="R6" t="n">
-        <v>7421176</v>
+        <v>7421272</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127351426</v>
+        <v>127351480</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863721</v>
+        <v>863715</v>
       </c>
       <c r="R7" t="n">
-        <v>7421272</v>
+        <v>7421176</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1657,32 +1657,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127350404</v>
+        <v>127350403</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>57821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>863898</v>
+        <v>863657</v>
       </c>
       <c r="R12" t="n">
-        <v>7420759</v>
+        <v>7421213</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1754,32 +1754,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127350403</v>
+        <v>127350404</v>
       </c>
       <c r="B13" t="n">
-        <v>57821</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>863657</v>
+        <v>863898</v>
       </c>
       <c r="R13" t="n">
-        <v>7421213</v>
+        <v>7420759</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -1757,7 +1757,7 @@
         <v>127350404</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127350421</v>
+        <v>127351442</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863799</v>
+        <v>863724</v>
       </c>
       <c r="R4" t="n">
-        <v>7421075</v>
+        <v>7421178</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,38 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R5" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127350411</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127350423</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,38 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R4" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350421</v>
+        <v>127351442</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,34 +977,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863799</v>
+        <v>863724</v>
       </c>
       <c r="R5" t="n">
-        <v>7421075</v>
+        <v>7421178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1070,7 +1070,7 @@
         <v>127351426</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127351480</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>127350422</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>127350424</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>127350410</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127350412</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127350403</v>
       </c>
       <c r="B12" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>127350404</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127350421</v>
+        <v>127351442</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863799</v>
+        <v>863724</v>
       </c>
       <c r="R4" t="n">
-        <v>7421075</v>
+        <v>7421178</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,38 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R5" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -1657,32 +1657,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127350403</v>
+        <v>127350404</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>98477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>863657</v>
+        <v>863898</v>
       </c>
       <c r="R12" t="n">
-        <v>7421213</v>
+        <v>7420759</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1754,32 +1754,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127350404</v>
+        <v>127350403</v>
       </c>
       <c r="B13" t="n">
-        <v>98471</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>863898</v>
+        <v>863657</v>
       </c>
       <c r="R13" t="n">
-        <v>7420759</v>
+        <v>7421213</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127350411</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127350423</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127351442</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127350421</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>127351426</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127351480</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>127350422</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>127350424</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>127350410</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127350412</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>127350404</v>
       </c>
       <c r="B12" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>127350403</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127350411</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127350423</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,38 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R4" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350421</v>
+        <v>127351442</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,34 +977,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863799</v>
+        <v>863724</v>
       </c>
       <c r="R5" t="n">
-        <v>7421075</v>
+        <v>7421178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1070,7 +1070,7 @@
         <v>127351426</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127351480</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>127350422</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>127350424</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>127350410</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>127350412</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,32 +1657,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127350404</v>
+        <v>127350403</v>
       </c>
       <c r="B12" t="n">
-        <v>98480</v>
+        <v>57832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>863898</v>
+        <v>863657</v>
       </c>
       <c r="R12" t="n">
-        <v>7420759</v>
+        <v>7421213</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1754,32 +1754,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127350403</v>
+        <v>127350404</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>98488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>863657</v>
+        <v>863898</v>
       </c>
       <c r="R13" t="n">
-        <v>7421213</v>
+        <v>7420759</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127350421</v>
+        <v>127351442</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863799</v>
+        <v>863724</v>
       </c>
       <c r="R4" t="n">
-        <v>7421075</v>
+        <v>7421178</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,38 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R5" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1757,7 +1757,7 @@
         <v>127350404</v>
       </c>
       <c r="B13" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,38 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R4" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350421</v>
+        <v>127351442</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,34 +977,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863799</v>
+        <v>863724</v>
       </c>
       <c r="R5" t="n">
-        <v>7421075</v>
+        <v>7421178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127350421</v>
+        <v>127351442</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863799</v>
+        <v>863724</v>
       </c>
       <c r="R4" t="n">
-        <v>7421075</v>
+        <v>7421178</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,38 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R5" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1657,32 +1657,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127350403</v>
+        <v>127350404</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>98490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>863657</v>
+        <v>863898</v>
       </c>
       <c r="R12" t="n">
-        <v>7421213</v>
+        <v>7420759</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1754,32 +1754,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127350404</v>
+        <v>127350403</v>
       </c>
       <c r="B13" t="n">
-        <v>98489</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>863898</v>
+        <v>863657</v>
       </c>
       <c r="R13" t="n">
-        <v>7420759</v>
+        <v>7421213</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,38 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R4" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350421</v>
+        <v>127351442</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,34 +977,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863799</v>
+        <v>863724</v>
       </c>
       <c r="R5" t="n">
-        <v>7421075</v>
+        <v>7421178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1660,7 +1660,7 @@
         <v>127350404</v>
       </c>
       <c r="B12" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127350411</v>
+        <v>127350410</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>863752</v>
+        <v>863776</v>
       </c>
       <c r="R2" t="n">
-        <v>7421058</v>
+        <v>7420960</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127350423</v>
+        <v>127350411</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>863918</v>
+        <v>863752</v>
       </c>
       <c r="R3" t="n">
-        <v>7420722</v>
+        <v>7421058</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127350421</v>
+        <v>127350412</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863799</v>
+        <v>863570</v>
       </c>
       <c r="R4" t="n">
-        <v>7421075</v>
+        <v>7421242</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,49 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127351442</v>
+        <v>127350421</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863724</v>
+        <v>863799</v>
       </c>
       <c r="R5" t="n">
-        <v>7421178</v>
+        <v>7421075</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1067,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127351426</v>
+        <v>127350422</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1096,22 +1092,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863721</v>
+        <v>863803</v>
       </c>
       <c r="R6" t="n">
-        <v>7421272</v>
+        <v>7421053</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1149,7 +1142,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1168,14 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127351480</v>
+        <v>127350423</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1197,19 +1189,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863715</v>
+        <v>863918</v>
       </c>
       <c r="R7" t="n">
-        <v>7421176</v>
+        <v>7420722</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1250,7 +1239,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127350422</v>
+        <v>127350424</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1304,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>863803</v>
+        <v>863943</v>
       </c>
       <c r="R8" t="n">
-        <v>7421053</v>
+        <v>7420707</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1366,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127350424</v>
+        <v>127351386</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1395,19 +1383,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>863943</v>
+        <v>863564</v>
       </c>
       <c r="R9" t="n">
-        <v>7420707</v>
+        <v>7421248</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1445,6 +1436,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1463,14 +1455,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127350410</v>
+        <v>127351426</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1492,19 +1484,22 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>863776</v>
+        <v>863721</v>
       </c>
       <c r="R10" t="n">
-        <v>7420960</v>
+        <v>7421272</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1542,6 +1537,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1560,14 +1556,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127350412</v>
+        <v>127351480</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1589,16 +1585,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>863570</v>
+        <v>863715</v>
       </c>
       <c r="R11" t="n">
-        <v>7421242</v>
+        <v>7421176</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1639,6 +1638,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1657,32 +1657,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127350404</v>
+        <v>127350403</v>
       </c>
       <c r="B12" t="n">
-        <v>98491</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>863898</v>
+        <v>863657</v>
       </c>
       <c r="R12" t="n">
-        <v>7420759</v>
+        <v>7421213</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1754,10 +1754,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127350403</v>
+        <v>127351442</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,16 +1783,20 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>863657</v>
+        <v>863724</v>
       </c>
       <c r="R13" t="n">
-        <v>7421213</v>
+        <v>7421178</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1848,6 +1852,103 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127350404</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kuusivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>863898</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7420759</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2948-2023 artfynd.xlsx
+++ b/artfynd/A 2948-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350410</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350411</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350421</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350422</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350423</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350424</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350404</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350412</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127351386</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127351426</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1751,6 +1806,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127351480</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350403</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1949,8 +2014,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127351442</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>